--- a/analysis/data/annotation/[Archived] Labeling SDG 2 - Benchmarking Dataset.xlsx
+++ b/analysis/data/annotation/[Archived] Labeling SDG 2 - Benchmarking Dataset.xlsx
@@ -12175,7 +12175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" hidden="1">
+    <row r="3">
       <c r="A3" s="34" t="s">
         <v>158</v>
       </c>
@@ -12245,7 +12245,7 @@
         <v>UNDECIDED</v>
       </c>
     </row>
-    <row r="4" hidden="1">
+    <row r="4">
       <c r="A4" s="34" t="s">
         <v>87</v>
       </c>
@@ -12857,7 +12857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" hidden="1">
+    <row r="13">
       <c r="A13" s="34" t="s">
         <v>156</v>
       </c>
@@ -12927,7 +12927,7 @@
         <v>UNDECIDED</v>
       </c>
     </row>
-    <row r="14" hidden="1">
+    <row r="14">
       <c r="A14" s="34" t="s">
         <v>257</v>
       </c>
@@ -13068,7 +13068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" hidden="1">
+    <row r="16">
       <c r="A16" s="34" t="s">
         <v>162</v>
       </c>
@@ -13138,7 +13138,7 @@
         <v>UNDECIDED</v>
       </c>
     </row>
-    <row r="17" hidden="1">
+    <row r="17">
       <c r="A17" s="34" t="s">
         <v>217</v>
       </c>
@@ -13276,7 +13276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" hidden="1">
+    <row r="19">
       <c r="A19" s="34" t="s">
         <v>131</v>
       </c>
@@ -13419,7 +13419,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" hidden="1">
+    <row r="21">
       <c r="A21" s="34" t="s">
         <v>199</v>
       </c>
@@ -13625,7 +13625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" hidden="1">
+    <row r="24">
       <c r="A24" s="34" t="s">
         <v>209</v>
       </c>
@@ -13761,7 +13761,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" hidden="1">
+    <row r="26">
       <c r="A26" s="34" t="s">
         <v>229</v>
       </c>
@@ -13831,7 +13831,7 @@
         <v>UNDECIDED</v>
       </c>
     </row>
-    <row r="27" hidden="1">
+    <row r="27">
       <c r="A27" s="34" t="s">
         <v>205</v>
       </c>
@@ -14377,7 +14377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" hidden="1">
+    <row r="35">
       <c r="A35" s="34" t="s">
         <v>211</v>
       </c>
@@ -14517,7 +14517,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" hidden="1">
+    <row r="37">
       <c r="A37" s="34" t="s">
         <v>242</v>
       </c>
@@ -14723,7 +14723,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" hidden="1">
+    <row r="40">
       <c r="A40" s="34" t="s">
         <v>166</v>
       </c>
@@ -14861,7 +14861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" hidden="1">
+    <row r="42">
       <c r="A42" s="34" t="s">
         <v>84</v>
       </c>
@@ -14931,7 +14931,7 @@
         <v>UNDECIDED</v>
       </c>
     </row>
-    <row r="43" hidden="1">
+    <row r="43">
       <c r="A43" s="34" t="s">
         <v>192</v>
       </c>
@@ -15139,7 +15139,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" hidden="1">
+    <row r="46">
       <c r="A46" s="34" t="s">
         <v>160</v>
       </c>
@@ -15753,7 +15753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" hidden="1">
+    <row r="55">
       <c r="A55" s="34" t="s">
         <v>135</v>
       </c>
@@ -16027,7 +16027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" hidden="1">
+    <row r="59">
       <c r="A59" s="34" t="s">
         <v>279</v>
       </c>
@@ -16301,7 +16301,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" hidden="1">
+    <row r="63">
       <c r="A63" s="34" t="s">
         <v>108</v>
       </c>
@@ -16374,7 +16374,7 @@
         <v>UNDECIDED</v>
       </c>
     </row>
-    <row r="64" hidden="1">
+    <row r="64">
       <c r="A64" s="34" t="s">
         <v>274</v>
       </c>
@@ -16648,7 +16648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" hidden="1">
+    <row r="68">
       <c r="A68" s="34" t="s">
         <v>203</v>
       </c>
@@ -16786,7 +16786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" hidden="1">
+    <row r="70">
       <c r="A70" s="34" t="s">
         <v>184</v>
       </c>
@@ -17194,7 +17194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" hidden="1">
+    <row r="76">
       <c r="A76" s="34" t="s">
         <v>233</v>
       </c>
@@ -17400,7 +17400,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" hidden="1">
+    <row r="79">
       <c r="A79" s="34" t="s">
         <v>110</v>
       </c>
@@ -17882,7 +17882,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" hidden="1">
+    <row r="86">
       <c r="A86" s="34" t="s">
         <v>186</v>
       </c>
@@ -18020,7 +18020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" hidden="1">
+    <row r="88">
       <c r="A88" s="34" t="s">
         <v>259</v>
       </c>
@@ -18090,7 +18090,7 @@
         <v>UNDECIDED</v>
       </c>
     </row>
-    <row r="89" hidden="1">
+    <row r="89">
       <c r="A89" s="34" t="s">
         <v>176</v>
       </c>
@@ -18160,7 +18160,7 @@
         <v>UNDECIDED</v>
       </c>
     </row>
-    <row r="90" hidden="1">
+    <row r="90">
       <c r="A90" s="34" t="s">
         <v>141</v>
       </c>
@@ -18364,7 +18364,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" hidden="1">
+    <row r="93">
       <c r="A93" s="34" t="s">
         <v>223</v>
       </c>
@@ -18915,7 +18915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" hidden="1">
+    <row r="101">
       <c r="A101" s="34" t="s">
         <v>265</v>
       </c>
@@ -18986,14 +18986,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="$A$1:$T$101">
-    <filterColumn colId="17">
-      <filters>
-        <filter val="TRUE"/>
-        <filter val="FALSE"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="$A$1:$T$101"/>
   <conditionalFormatting sqref="C2:H101 J2:Q101">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"TRUE"</formula>
